--- a/sample/docs/tabular/reserve-register.xlsx
+++ b/sample/docs/tabular/reserve-register.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="€#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -470,31 +470,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C-1002</t>
+          <t>C-1001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PA-0000002</t>
+          <t>HH-0000004</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Personal Auto</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AD-002</t>
+          <t>AD-001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>28900</v>
+        <v>49900</v>
       </c>
     </row>
     <row r="4">
@@ -505,26 +505,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PA-0000005</t>
+          <t>HH-0000004</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Personal Auto</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AD-002</t>
+          <t>AD-001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>18350</v>
+        <v>12850</v>
       </c>
     </row>
   </sheetData>

--- a/sample/docs/tabular/reserve-register.xlsx
+++ b/sample/docs/tabular/reserve-register.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,12 +475,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HH-0000004</t>
+          <t>COM-0000004</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -490,41 +490,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>49900</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C-1004</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HH-0000004</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Household</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AD-001</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>12850</v>
+        <v>53950</v>
       </c>
     </row>
   </sheetData>

--- a/sample/docs/tabular/reserve-register.xlsx
+++ b/sample/docs/tabular/reserve-register.xlsx
@@ -475,26 +475,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>COM-0000004</t>
+          <t>HH-0000001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AD-001</t>
+          <t>AD-002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>53950</v>
+        <v>12850</v>
       </c>
     </row>
   </sheetData>

--- a/sample/docs/tabular/reserve-register.xlsx
+++ b/sample/docs/tabular/reserve-register.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HH-0000004</t>
+          <t>HH-0000001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,45 +485,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AD-001</t>
+          <t>AD-002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>49900</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C-1004</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HH-0000004</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Household</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AD-001</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
         <v>12850</v>
       </c>
     </row>

--- a/sample/docs/tabular/reserve-register.xlsx
+++ b/sample/docs/tabular/reserve-register.xlsx
@@ -475,12 +475,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HH-0000001</t>
+          <t>MOT-0000002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Motor</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -490,11 +490,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>12850</v>
+        <v>2050</v>
       </c>
     </row>
   </sheetData>
